--- a/output/銀行開戶總表.xlsx
+++ b/output/銀行開戶總表.xlsx
@@ -71,7 +71,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="007F7F7F"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,10 +106,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -122,8 +122,8 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -510,101 +510,97 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>財務部自營（銀行自有資金）　（9 家）</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>一、已開戶　（24 家）</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>華南銀行</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>有開戶（TMU 透過財務部下單）</t>
-        </is>
-      </c>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　財務部自營（銀行自有資金）　（9 家）</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>第一商業銀行</t>
+          <t>華南銀行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>有股票戶、尚無債券交易；該行 TMU 不做交易</t>
+          <t>有開戶（TMU 透過財務部下單）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>京城銀行</t>
+          <t>第一商業銀行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>有開戶</t>
+          <t>有股票戶、尚無債券交易；該行 TMU 不做交易</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>華泰商業銀行</t>
+          <t>京城銀行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>有開戶、久未交易</t>
+          <t>有開戶</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>高雄銀行</t>
+          <t>華泰商業銀行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>有開戶</t>
+          <t>有開戶、久未交易</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>瑞興商業銀行</t>
+          <t>高雄銀行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>已連繫</t>
+          <t>有開戶</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>陽信商業銀行</t>
+          <t>瑞興商業銀行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>有交易往來</t>
+          <t>已連繫</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>板信商銀</t>
+          <t>陽信商業銀行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -616,39 +612,39 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>板信商銀</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>有交易往來</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>臺灣中小企業銀行</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>已取得債券授權交易</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>總行 TMU（資金來自客戶）　（11 家）</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>聯邦銀行</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>有交易往來</t>
-        </is>
-      </c>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　總行 TMU（資金來自客戶）　（11 家）</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>星展銀行</t>
+          <t>聯邦銀行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -660,7 +656,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>台新銀行</t>
+          <t>星展銀行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -672,7 +668,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>元大商業銀行</t>
+          <t>台新銀行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -684,7 +680,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>王道商業銀行</t>
+          <t>元大商業銀行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -696,7 +692,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>新光銀行</t>
+          <t>王道商業銀行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -708,99 +704,99 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>合庫銀行</t>
+          <t>新光銀行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>有主帳，需新增子帳</t>
+          <t>有交易往來</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>兆豐銀行</t>
+          <t>合庫銀行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>有交易往來</t>
+          <t>有主帳，需新增子帳</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>安泰銀行</t>
+          <t>兆豐銀行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>有開戶；新負責人不願提供 ID</t>
+          <t>有交易往來</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>上海銀行</t>
+          <t>安泰銀行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>目前僅開亞灣區</t>
+          <t>有開戶；新負責人不願提供 ID</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t>上海銀行</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>目前僅開亞灣區</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t>永豐銀行</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>TMU 接觸中；信託部已開戶</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>B2B 已開戶（另一通路）　（4 家）</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n"/>
-    </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>凱基商業銀行</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>B2B 已開戶（總行 TIS，與信託/財務部無關）</t>
-        </is>
-      </c>
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　B2B 已開戶（另一通路）　（4 家）</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>渣打國際商業銀行</t>
+          <t>凱基商業銀行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>B2B 已開戶</t>
+          <t>B2B 已開戶（總行 TIS，與信託/財務部無關）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>三信商業銀行</t>
+          <t>渣打國際商業銀行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -812,75 +808,75 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
+          <t>三信商業銀行</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>B2B 已開戶</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
           <t>匯豐(台灣)銀行</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>B2B 已開戶</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>未開戶／洽談中　（12 家）</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n"/>
-    </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>台北富邦銀行</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>已拜訪財務部 &amp; TMU</t>
-        </is>
-      </c>
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>二、未開戶／洽談中　（12 家）</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>中國信託商業銀行</t>
+          <t>台北富邦銀行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>已拜訪 TMU</t>
+          <t>已拜訪財務部 &amp; TMU</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>遠東國際商業銀行</t>
+          <t>中國信託商業銀行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>已拜訪財務部 &amp; 信託基金</t>
+          <t>已拜訪 TMU</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>彰化商業銀行</t>
+          <t>遠東國際商業銀行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>已拜訪財務部</t>
+          <t>已拜訪財務部 &amp; 信託基金</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>玉山商業銀行</t>
+          <t>彰化商業銀行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -892,67 +888,67 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>中華郵政</t>
+          <t>玉山商業銀行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>已連繫，待下次遴選</t>
+          <t>已拜訪財務部</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>臺灣銀行</t>
+          <t>中華郵政</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>待聯繫</t>
+          <t>已連繫，待下次遴選</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>臺灣土地銀行</t>
+          <t>臺灣銀行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>可透過自營（不提供負責人 ID）</t>
+          <t>待聯繫</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>台中商業銀行</t>
+          <t>臺灣土地銀行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>已聯繫，目前不開戶</t>
+          <t>可透過自營（不提供負責人 ID）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>連線銀行</t>
+          <t>台中商業銀行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>目前不開複委託</t>
+          <t>已聯繫，目前不開戶</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>將來銀行</t>
+          <t>連線銀行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -964,21 +960,34 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
+          <t>將來銀行</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>目前不開複委託</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>樂天銀行</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>目前不做外幣債</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A24:B24"/>
+  <mergeCells count="5">
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
